--- a/Weights, Max Units and Printer for CSV routing.xlsx
+++ b/Weights, Max Units and Printer for CSV routing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002DD742-492E-4AB4-A46F-5F2D80DBE4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B33A0-18F1-4EA5-9A18-8B1B58923F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
+    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="166">
   <si>
     <t>SKU</t>
   </si>
@@ -478,6 +478,51 @@
   </si>
   <si>
     <t>Handozer</t>
+  </si>
+  <si>
+    <t>Ez Pole</t>
+  </si>
+  <si>
+    <t>EZD17</t>
+  </si>
+  <si>
+    <t>EZD21</t>
+  </si>
+  <si>
+    <t>EZC17</t>
+  </si>
+  <si>
+    <t>EZC21</t>
+  </si>
+  <si>
+    <t>EZL17</t>
+  </si>
+  <si>
+    <t>EZL21</t>
+  </si>
+  <si>
+    <t>EZL21B</t>
+  </si>
+  <si>
+    <t>EZAA25</t>
+  </si>
+  <si>
+    <t>EZAA30</t>
+  </si>
+  <si>
+    <t>EZTHWF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZTH </t>
+  </si>
+  <si>
+    <t>EZRMWF</t>
+  </si>
+  <si>
+    <t>RV21C</t>
+  </si>
+  <si>
+    <t>RV21D</t>
   </si>
 </sst>
 </file>
@@ -832,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F995FDA-EC34-42E7-A8C6-E6CA5B8CE506}">
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1149,10 +1194,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B19">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1161,83 +1206,83 @@
         <v>136</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>136</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>136</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1246,15 +1291,15 @@
         <v>136</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="B25">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1263,15 +1308,15 @@
         <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="B26">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1280,15 +1325,15 @@
         <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="B27">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1297,15 +1342,15 @@
         <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1314,15 +1359,15 @@
         <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="B29">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1331,15 +1376,15 @@
         <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="B30">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1348,15 +1393,15 @@
         <v>136</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="B31">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1365,15 +1410,15 @@
         <v>136</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B32">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1382,15 +1427,15 @@
         <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="B33">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1399,83 +1444,83 @@
         <v>136</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B34">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
         <v>136</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
         <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B37">
         <v>18</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
         <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B38">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1484,15 +1529,15 @@
         <v>136</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B39">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1506,10 +1551,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B40">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1523,10 +1568,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1540,10 +1585,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1557,10 +1602,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1574,95 +1619,95 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>136</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45" t="s">
         <v>136</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D46" t="s">
         <v>136</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>136</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B48">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
         <v>136</v>
       </c>
       <c r="E48" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B49">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1671,49 +1716,49 @@
         <v>136</v>
       </c>
       <c r="E49" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>136</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B51">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="s">
         <v>136</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B52">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1722,66 +1767,66 @@
         <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
         <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>136</v>
       </c>
       <c r="E55" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="B56">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1790,15 +1835,15 @@
         <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="B57">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1807,100 +1852,100 @@
         <v>136</v>
       </c>
       <c r="E57" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B58">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D58" t="s">
         <v>136</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B59">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" t="s">
         <v>136</v>
       </c>
       <c r="E59" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B60">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60" t="s">
         <v>136</v>
       </c>
       <c r="E60" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B61">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" t="s">
         <v>136</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B62">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
         <v>136</v>
       </c>
       <c r="E62" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B63">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1909,49 +1954,49 @@
         <v>136</v>
       </c>
       <c r="E63" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B64">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D64" t="s">
         <v>136</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B65">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="s">
         <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B66">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -1960,505 +2005,505 @@
         <v>136</v>
       </c>
       <c r="E66" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B67">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D67" t="s">
         <v>136</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B68">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D68" t="s">
         <v>136</v>
       </c>
       <c r="E68" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B69">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D69" t="s">
         <v>136</v>
       </c>
       <c r="E69" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C70">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E72" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B73">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B74">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B75">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E75" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B77">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E77" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B78">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B79">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E79" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B81">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E81" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B82">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E82" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B83">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E83" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="B84">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
         <v>138</v>
       </c>
       <c r="E84" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D85" t="s">
         <v>138</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D86" t="s">
         <v>138</v>
       </c>
       <c r="E86" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
         <v>138</v>
       </c>
       <c r="E87" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>6102</v>
+      <c r="A88" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
         <v>138</v>
       </c>
       <c r="E88" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>6106</v>
+      <c r="A89" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B89">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
         <v>138</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B90">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
         <v>138</v>
       </c>
       <c r="E90" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D91" t="s">
         <v>138</v>
       </c>
       <c r="E91" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
         <v>138</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
         <v>138</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
         <v>138</v>
       </c>
       <c r="E94" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95" t="s">
         <v>138</v>
       </c>
       <c r="E95" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="B96">
         <v>14</v>
@@ -2475,265 +2520,265 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
         <v>138</v>
       </c>
       <c r="E97" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C98">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D98" t="s">
         <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="B99">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
         <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D100" t="s">
         <v>138</v>
       </c>
       <c r="E100" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D101" t="s">
         <v>138</v>
       </c>
       <c r="E101" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>108</v>
+      <c r="A102" s="1">
+        <v>6102</v>
       </c>
       <c r="B102">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
         <v>138</v>
       </c>
       <c r="E102" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>107</v>
+      <c r="A103" s="1">
+        <v>6106</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C103">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D103" t="s">
         <v>138</v>
       </c>
       <c r="E103" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
         <v>138</v>
       </c>
       <c r="E104" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D105" t="s">
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B106">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C106">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D106" t="s">
         <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B107">
         <v>5</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" t="s">
         <v>138</v>
       </c>
       <c r="E107" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" t="s">
         <v>138</v>
       </c>
       <c r="E108" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" t="s">
         <v>138</v>
       </c>
       <c r="E109" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C110">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
         <v>138</v>
       </c>
       <c r="E110" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C111">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D111" t="s">
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C112">
         <v>12</v>
@@ -2742,80 +2787,80 @@
         <v>138</v>
       </c>
       <c r="E112" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C113">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D113" t="s">
         <v>138</v>
       </c>
       <c r="E113" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D114" t="s">
         <v>138</v>
       </c>
       <c r="E114" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C115">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D115" t="s">
         <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C116">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D116" t="s">
         <v>138</v>
       </c>
       <c r="E116" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2827,193 +2872,431 @@
         <v>138</v>
       </c>
       <c r="E117" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
         <v>138</v>
       </c>
       <c r="E118" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C119">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D119" t="s">
         <v>138</v>
       </c>
       <c r="E119" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C120">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D120" t="s">
         <v>138</v>
       </c>
       <c r="E120" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C121">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D121" t="s">
         <v>138</v>
       </c>
       <c r="E121" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D122" t="s">
         <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D123" t="s">
         <v>138</v>
       </c>
       <c r="E123" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
         <v>138</v>
       </c>
       <c r="E124" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D125" t="s">
         <v>138</v>
       </c>
       <c r="E125" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D126" t="s">
         <v>138</v>
       </c>
       <c r="E126" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D127" t="s">
         <v>138</v>
       </c>
       <c r="E127" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
+        <v>138</v>
+      </c>
+      <c r="E128" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>138</v>
+      </c>
+      <c r="E129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
+        <v>138</v>
+      </c>
+      <c r="E130" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>12</v>
+      </c>
+      <c r="D131" t="s">
+        <v>138</v>
+      </c>
+      <c r="E131" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>12</v>
+      </c>
+      <c r="D132" t="s">
+        <v>138</v>
+      </c>
+      <c r="E132" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>12</v>
+      </c>
+      <c r="D133" t="s">
+        <v>138</v>
+      </c>
+      <c r="E133" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>12</v>
+      </c>
+      <c r="D134" t="s">
+        <v>138</v>
+      </c>
+      <c r="E134" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>12</v>
+      </c>
+      <c r="D135" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>12</v>
+      </c>
+      <c r="D136" t="s">
+        <v>138</v>
+      </c>
+      <c r="E136" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B137">
+        <v>5</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="s">
+        <v>138</v>
+      </c>
+      <c r="E137" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>138</v>
+      </c>
+      <c r="E138" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>138</v>
+      </c>
+      <c r="E139" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="s">
+        <v>138</v>
+      </c>
+      <c r="E140" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141" t="s">
+        <v>138</v>
+      </c>
+      <c r="E141" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B128">
-        <v>1</v>
-      </c>
-      <c r="C128">
-        <v>5</v>
-      </c>
-      <c r="D128" t="s">
-        <v>138</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>138</v>
+      </c>
+      <c r="E142" t="s">
         <v>135</v>
       </c>
     </row>

--- a/Weights, Max Units and Printer for CSV routing.xlsx
+++ b/Weights, Max Units and Printer for CSV routing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B33A0-18F1-4EA5-9A18-8B1B58923F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5A3FB9-AD1A-4D46-AA92-BC81B59487B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="173">
   <si>
     <t>SKU</t>
   </si>
@@ -523,6 +523,27 @@
   </si>
   <si>
     <t>RV21D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added Description with PO# </t>
+  </si>
+  <si>
+    <t>Coarse 10</t>
+  </si>
+  <si>
+    <t>Fine 10</t>
+  </si>
+  <si>
+    <t>Medium 10</t>
+  </si>
+  <si>
+    <t>Coarse 25</t>
+  </si>
+  <si>
+    <t>Fine 25</t>
+  </si>
+  <si>
+    <t>Medium 25</t>
   </si>
 </sst>
 </file>
@@ -877,16 +898,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F995FDA-EC34-42E7-A8C6-E6CA5B8CE506}">
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -902,8 +924,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -919,8 +944,11 @@
       <c r="E2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>143</v>
       </c>
@@ -936,8 +964,11 @@
       <c r="E3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>144</v>
       </c>
@@ -953,8 +984,11 @@
       <c r="E4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>145</v>
       </c>
@@ -970,8 +1004,11 @@
       <c r="E5" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -987,8 +1024,11 @@
       <c r="E6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -1004,8 +1044,11 @@
       <c r="E7" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1022,7 +1065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1039,7 +1082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1056,7 +1099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1073,7 +1116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,7 +1133,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,7 +1150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +1167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1141,7 +1184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>

--- a/Weights, Max Units and Printer for CSV routing.xlsx
+++ b/Weights, Max Units and Printer for CSV routing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\Order-Splitter-v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5A3FB9-AD1A-4D46-AA92-BC81B59487B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD6779-3740-4E55-8737-D0BBDA922FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
   </bookViews>
@@ -1903,7 +1903,7 @@
         <v>44</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>5</v>

--- a/Weights, Max Units and Printer for CSV routing.xlsx
+++ b/Weights, Max Units and Printer for CSV routing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\Order-Splitter-v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD6779-3740-4E55-8737-D0BBDA922FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745F51D6-F22A-4D88-8014-360F6C6F412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
   </bookViews>
@@ -1906,7 +1906,7 @@
         <v>2</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="s">
         <v>136</v>

--- a/Weights, Max Units and Printer for CSV routing.xlsx
+++ b/Weights, Max Units and Printer for CSV routing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\Order-Splitter-v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745F51D6-F22A-4D88-8014-360F6C6F412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68BA17F-23FF-47F9-965E-A3FA4F838805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{A76D3FB3-0073-4C27-B24A-D444BD4B1079}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="184">
   <si>
     <t>SKU</t>
   </si>
@@ -544,6 +544,39 @@
   </si>
   <si>
     <t>Medium 25</t>
+  </si>
+  <si>
+    <t>PCAP44</t>
+  </si>
+  <si>
+    <t>PCAP66</t>
+  </si>
+  <si>
+    <t>4442C12</t>
+  </si>
+  <si>
+    <t>4642C8</t>
+  </si>
+  <si>
+    <t>6642C6</t>
+  </si>
+  <si>
+    <t>6660C6</t>
+  </si>
+  <si>
+    <t>Post Protector</t>
+  </si>
+  <si>
+    <t>SBP99</t>
+  </si>
+  <si>
+    <t>Post Protector SBP99</t>
+  </si>
+  <si>
+    <t>Min Unit per box</t>
+  </si>
+  <si>
+    <t>Box Weight</t>
   </si>
 </sst>
 </file>
@@ -579,9 +612,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -898,17 +934,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F995FDA-EC34-42E7-A8C6-E6CA5B8CE506}">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -916,2430 +954,3233 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>142</v>
       </c>
       <c r="B2">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" t="s">
         <v>148</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>143</v>
       </c>
       <c r="B3">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" t="s">
         <v>148</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>144</v>
       </c>
       <c r="B4">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" t="s">
         <v>148</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>145</v>
       </c>
       <c r="B5">
         <v>26</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" t="s">
         <v>148</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>146</v>
       </c>
       <c r="B6">
         <v>26</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" t="s">
         <v>148</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
       <c r="B7">
         <v>26</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" t="s">
         <v>148</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>137</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>137</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>2</v>
       </c>
-      <c r="D13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="D16" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>2</v>
       </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
         <v>2</v>
       </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>136</v>
+      </c>
+      <c r="G18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B19">
         <v>13</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B20">
         <v>14</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B21">
         <v>13</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B22">
         <v>14</v>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B23">
         <v>14</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B24">
         <v>18</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B25">
         <v>18</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>159</v>
       </c>
       <c r="B26">
         <v>31</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>160</v>
       </c>
       <c r="B27">
         <v>38</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B28">
         <v>16</v>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B29">
         <v>16</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>163</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B31">
         <v>14</v>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B32">
         <v>14</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>136</v>
+      </c>
+      <c r="G32" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B33">
         <v>82</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>136</v>
+      </c>
+      <c r="G33" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34">
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
         <v>12</v>
       </c>
-      <c r="D34" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>136</v>
+      </c>
+      <c r="G34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B35">
         <v>14</v>
       </c>
-      <c r="C35">
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>136</v>
+      </c>
+      <c r="G35" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B36">
         <v>9</v>
       </c>
-      <c r="C36">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
         <v>4</v>
       </c>
-      <c r="D36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>136</v>
+      </c>
+      <c r="G36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B37">
         <v>18</v>
       </c>
-      <c r="C37">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
         <v>2</v>
       </c>
-      <c r="D37" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B38">
         <v>36</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B39">
         <v>28</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G39" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B40">
         <v>23</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B41">
         <v>26</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B42">
         <v>26</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B43">
         <v>25</v>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>136</v>
+      </c>
+      <c r="G43" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B44">
         <v>25</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B45">
         <v>32</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G45" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B46">
         <v>32</v>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B47">
         <v>41</v>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B48">
         <v>41</v>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>136</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>136</v>
+      </c>
+      <c r="G48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B49">
         <v>20</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>136</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>136</v>
+      </c>
+      <c r="G49" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B50">
         <v>20</v>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B51">
         <v>18</v>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>136</v>
+      </c>
+      <c r="G51" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B52">
         <v>18</v>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G52" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B53">
         <v>18</v>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>136</v>
+      </c>
+      <c r="G53" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B54">
         <v>18</v>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>136</v>
+      </c>
+      <c r="G54" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B55">
         <v>5</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>136</v>
+      </c>
+      <c r="G55" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>136</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>136</v>
+      </c>
+      <c r="G56" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>136</v>
+      </c>
+      <c r="G57" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="C58">
         <v>4</v>
       </c>
-      <c r="D58" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>30</v>
+      </c>
+      <c r="F58" t="s">
+        <v>136</v>
+      </c>
+      <c r="G58" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>30</v>
+      </c>
+      <c r="F59" t="s">
+        <v>136</v>
+      </c>
+      <c r="G59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>4430</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>136</v>
+      </c>
+      <c r="G60" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>4442</v>
+      </c>
+      <c r="C61">
+        <v>12</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>136</v>
+      </c>
+      <c r="G61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C62">
+        <v>24</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>136</v>
+      </c>
+      <c r="G62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>4642</v>
+      </c>
+      <c r="C63">
+        <v>24</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63" t="s">
+        <v>136</v>
+      </c>
+      <c r="G63" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64">
+        <v>24</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>136</v>
+      </c>
+      <c r="G64" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>4660</v>
+      </c>
+      <c r="C65">
+        <v>12</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+      <c r="F65" t="s">
+        <v>136</v>
+      </c>
+      <c r="G65" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>6630</v>
+      </c>
+      <c r="C66">
+        <v>10</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>6</v>
+      </c>
+      <c r="F66" t="s">
+        <v>136</v>
+      </c>
+      <c r="G66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>6642</v>
+      </c>
+      <c r="C67">
+        <v>12</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>136</v>
+      </c>
+      <c r="G67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68">
+        <v>24</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>136</v>
+      </c>
+      <c r="G68" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>6660</v>
+      </c>
+      <c r="C69">
+        <v>12</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69" t="s">
+        <v>136</v>
+      </c>
+      <c r="G69" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C70">
+        <v>24</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G70" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>8860</v>
+      </c>
+      <c r="C71">
+        <v>24</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
+        <v>136</v>
+      </c>
+      <c r="G71" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>4442</v>
+      </c>
+      <c r="C72">
+        <v>24</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>136</v>
+      </c>
+      <c r="G72" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>4660</v>
+      </c>
+      <c r="C73">
+        <v>24</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>9</v>
+      </c>
+      <c r="F73" t="s">
+        <v>136</v>
+      </c>
+      <c r="G73" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>6642</v>
+      </c>
+      <c r="C74">
+        <v>24</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74" t="s">
+        <v>136</v>
+      </c>
+      <c r="G74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>6660</v>
+      </c>
+      <c r="C75">
+        <v>24</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>6</v>
+      </c>
+      <c r="F75" t="s">
+        <v>136</v>
+      </c>
+      <c r="G75" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77" t="s">
+        <v>136</v>
+      </c>
+      <c r="G77" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B59">
+      <c r="B78">
         <v>5</v>
       </c>
-      <c r="C59">
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
         <v>5</v>
       </c>
-      <c r="D59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="F78" t="s">
+        <v>136</v>
+      </c>
+      <c r="G78" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B60">
+      <c r="B79">
         <v>5</v>
       </c>
-      <c r="C60">
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
         <v>5</v>
       </c>
-      <c r="D60" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F79" t="s">
+        <v>136</v>
+      </c>
+      <c r="G79" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B61">
+      <c r="B80">
         <v>8</v>
       </c>
-      <c r="C61">
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
         <v>4</v>
       </c>
-      <c r="D61" t="s">
-        <v>136</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F80" t="s">
+        <v>136</v>
+      </c>
+      <c r="G80" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B62">
+      <c r="B81">
         <v>16</v>
       </c>
-      <c r="C62">
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
         <v>2</v>
       </c>
-      <c r="D62" t="s">
-        <v>136</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F81" t="s">
+        <v>136</v>
+      </c>
+      <c r="G81" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B63">
+      <c r="B82">
         <v>32</v>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82" t="s">
+        <v>136</v>
+      </c>
+      <c r="G82" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B64">
+      <c r="B83">
         <v>10</v>
       </c>
-      <c r="C64">
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
         <v>4</v>
       </c>
-      <c r="D64" t="s">
-        <v>136</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F83" t="s">
+        <v>136</v>
+      </c>
+      <c r="G83" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B65">
+      <c r="B84">
         <v>20</v>
       </c>
-      <c r="C65">
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
         <v>2</v>
       </c>
-      <c r="D65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F84" t="s">
+        <v>136</v>
+      </c>
+      <c r="G84" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B66">
+      <c r="B85">
         <v>30</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
-        <v>136</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>136</v>
+      </c>
+      <c r="G85" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B67">
+      <c r="B86">
         <v>3</v>
       </c>
-      <c r="C67">
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
         <v>4</v>
       </c>
-      <c r="D67" t="s">
-        <v>136</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F86" t="s">
+        <v>136</v>
+      </c>
+      <c r="G86" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B68">
+      <c r="B87">
         <v>3</v>
       </c>
-      <c r="C68">
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
         <v>4</v>
       </c>
-      <c r="D68" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F87" t="s">
+        <v>136</v>
+      </c>
+      <c r="G87" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B69">
+      <c r="B88">
         <v>4</v>
       </c>
-      <c r="C69">
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
         <v>4</v>
       </c>
-      <c r="D69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F88" t="s">
+        <v>136</v>
+      </c>
+      <c r="G88" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B70">
+      <c r="B89">
         <v>18</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>136</v>
+      </c>
+      <c r="G89" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B71">
+      <c r="B90">
         <v>18</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71" t="s">
-        <v>136</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>136</v>
+      </c>
+      <c r="G90" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B72">
+      <c r="B91">
         <v>18</v>
       </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72" t="s">
-        <v>136</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>136</v>
+      </c>
+      <c r="G91" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B73">
+      <c r="B92">
         <v>18</v>
       </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73" t="s">
-        <v>136</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>136</v>
+      </c>
+      <c r="G92" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B74">
+      <c r="B93">
         <v>18</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74" t="s">
-        <v>136</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>136</v>
+      </c>
+      <c r="G93" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B75">
+      <c r="B94">
         <v>18</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>136</v>
+      </c>
+      <c r="G94" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B76">
+      <c r="B95">
         <v>18</v>
       </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76" t="s">
-        <v>136</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>136</v>
+      </c>
+      <c r="G95" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B77">
+      <c r="B96">
         <v>18</v>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77" t="s">
-        <v>136</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>136</v>
+      </c>
+      <c r="G96" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B78">
+      <c r="B97">
         <v>18</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" t="s">
-        <v>136</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>136</v>
+      </c>
+      <c r="G97" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B79">
+      <c r="B98">
         <v>18</v>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" t="s">
-        <v>136</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>136</v>
+      </c>
+      <c r="G98" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B80">
+      <c r="B99">
         <v>18</v>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G99" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B81">
+      <c r="B100">
         <v>18</v>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
-        <v>136</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>136</v>
+      </c>
+      <c r="G100" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B82">
+      <c r="B101">
         <v>18</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>136</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>136</v>
+      </c>
+      <c r="G101" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B83">
+      <c r="B102">
         <v>18</v>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>136</v>
+      </c>
+      <c r="G102" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
         <v>20</v>
       </c>
-      <c r="D84" t="s">
-        <v>138</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F103" t="s">
+        <v>138</v>
+      </c>
+      <c r="G103" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B85">
+      <c r="B104">
         <v>2</v>
       </c>
-      <c r="C85">
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
         <v>20</v>
       </c>
-      <c r="D85" t="s">
-        <v>138</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F104" t="s">
+        <v>138</v>
+      </c>
+      <c r="G104" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
         <v>5</v>
       </c>
-      <c r="D86" t="s">
-        <v>138</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F105" t="s">
+        <v>138</v>
+      </c>
+      <c r="G105" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87">
+      <c r="B106">
         <v>14</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
-        <v>138</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>138</v>
+      </c>
+      <c r="G106" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B88">
+      <c r="B107">
         <v>14</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
-        <v>138</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
+        <v>138</v>
+      </c>
+      <c r="G107" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B89">
+      <c r="B108">
         <v>14</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
-        <v>138</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>138</v>
+      </c>
+      <c r="G108" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B90">
+      <c r="B109">
         <v>24</v>
       </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90" t="s">
-        <v>138</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>138</v>
+      </c>
+      <c r="G109" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B91">
-        <v>14</v>
-      </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91" t="s">
-        <v>138</v>
-      </c>
-      <c r="E91" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B92">
-        <v>24</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>138</v>
-      </c>
-      <c r="E92" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B93">
-        <v>14</v>
-      </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-      <c r="D93" t="s">
-        <v>138</v>
-      </c>
-      <c r="E93" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B94">
-        <v>14</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94" t="s">
-        <v>138</v>
-      </c>
-      <c r="E94" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B95">
-        <v>14</v>
-      </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95" t="s">
-        <v>138</v>
-      </c>
-      <c r="E95" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96">
-        <v>14</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96" t="s">
-        <v>138</v>
-      </c>
-      <c r="E96" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B97">
-        <v>14</v>
-      </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97" t="s">
-        <v>138</v>
-      </c>
-      <c r="E97" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B98">
-        <v>24</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>138</v>
-      </c>
-      <c r="E98" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B99">
-        <v>24</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
-        <v>138</v>
-      </c>
-      <c r="E99" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100">
-        <v>10</v>
-      </c>
-      <c r="D100" t="s">
-        <v>138</v>
-      </c>
-      <c r="E100" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B101">
-        <v>2</v>
-      </c>
-      <c r="C101">
-        <v>10</v>
-      </c>
-      <c r="D101" t="s">
-        <v>138</v>
-      </c>
-      <c r="E101" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>6102</v>
-      </c>
-      <c r="B102">
-        <v>5</v>
-      </c>
-      <c r="C102">
-        <v>2</v>
-      </c>
-      <c r="D102" t="s">
-        <v>138</v>
-      </c>
-      <c r="E102" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>6106</v>
-      </c>
-      <c r="B103">
-        <v>8</v>
-      </c>
-      <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
-        <v>138</v>
-      </c>
-      <c r="E103" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B104">
-        <v>5</v>
-      </c>
-      <c r="C104">
-        <v>5</v>
-      </c>
-      <c r="D104" t="s">
-        <v>138</v>
-      </c>
-      <c r="E104" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B105">
-        <v>5</v>
-      </c>
-      <c r="C105">
-        <v>5</v>
-      </c>
-      <c r="D105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E105" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B106">
-        <v>5</v>
-      </c>
-      <c r="C106">
-        <v>5</v>
-      </c>
-      <c r="D106" t="s">
-        <v>138</v>
-      </c>
-      <c r="E106" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107">
-        <v>5</v>
-      </c>
-      <c r="C107">
-        <v>5</v>
-      </c>
-      <c r="D107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E107" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B108">
-        <v>5</v>
-      </c>
-      <c r="C108">
-        <v>5</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B109">
-        <v>5</v>
-      </c>
-      <c r="C109">
-        <v>5</v>
-      </c>
-      <c r="D109" t="s">
-        <v>138</v>
-      </c>
-      <c r="E109" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="B110">
         <v>14</v>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110" t="s">
-        <v>138</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
+        <v>138</v>
+      </c>
+      <c r="G110" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B111">
-        <v>9</v>
-      </c>
-      <c r="C111">
-        <v>4</v>
-      </c>
-      <c r="D111" t="s">
-        <v>138</v>
-      </c>
-      <c r="E111" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>138</v>
+      </c>
+      <c r="G111" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="B112">
-        <v>5</v>
-      </c>
-      <c r="C112">
-        <v>12</v>
-      </c>
-      <c r="D112" t="s">
-        <v>138</v>
-      </c>
-      <c r="E112" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+      <c r="F112" t="s">
+        <v>138</v>
+      </c>
+      <c r="G112" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="B113">
-        <v>9</v>
-      </c>
-      <c r="C113">
-        <v>4</v>
-      </c>
-      <c r="D113" t="s">
-        <v>138</v>
-      </c>
-      <c r="E113" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113" t="s">
+        <v>138</v>
+      </c>
+      <c r="G113" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B114">
+        <v>14</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114" t="s">
+        <v>138</v>
+      </c>
+      <c r="G114" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B115">
+        <v>14</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>138</v>
+      </c>
+      <c r="G115" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B116">
+        <v>14</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" t="s">
+        <v>138</v>
+      </c>
+      <c r="G116" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B117">
+        <v>24</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117" t="s">
+        <v>138</v>
+      </c>
+      <c r="G117" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B118">
+        <v>24</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118" t="s">
+        <v>138</v>
+      </c>
+      <c r="G118" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s">
+        <v>138</v>
+      </c>
+      <c r="G119" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B120">
         <v>2</v>
       </c>
-      <c r="C114">
-        <v>5</v>
-      </c>
-      <c r="D114" t="s">
-        <v>138</v>
-      </c>
-      <c r="E114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B115">
-        <v>5</v>
-      </c>
-      <c r="C115">
-        <v>6</v>
-      </c>
-      <c r="D115" t="s">
-        <v>138</v>
-      </c>
-      <c r="E115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B116">
-        <v>9</v>
-      </c>
-      <c r="C116">
-        <v>4</v>
-      </c>
-      <c r="D116" t="s">
-        <v>138</v>
-      </c>
-      <c r="E116" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B117">
-        <v>1</v>
-      </c>
-      <c r="C117">
-        <v>12</v>
-      </c>
-      <c r="D117" t="s">
-        <v>138</v>
-      </c>
-      <c r="E117" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118">
-        <v>8</v>
-      </c>
-      <c r="D118" t="s">
-        <v>138</v>
-      </c>
-      <c r="E118" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B119">
-        <v>4</v>
-      </c>
-      <c r="C119">
-        <v>6</v>
-      </c>
-      <c r="D119" t="s">
-        <v>138</v>
-      </c>
-      <c r="E119" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B120">
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
         <v>10</v>
       </c>
-      <c r="C120">
-        <v>4</v>
-      </c>
-      <c r="D120" t="s">
-        <v>138</v>
-      </c>
-      <c r="E120" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>103</v>
+      <c r="F120" t="s">
+        <v>138</v>
+      </c>
+      <c r="G120" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>6102</v>
       </c>
       <c r="B121">
         <v>5</v>
       </c>
-      <c r="C121">
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>138</v>
+      </c>
+      <c r="G121" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>6106</v>
+      </c>
+      <c r="B122">
+        <v>8</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>138</v>
+      </c>
+      <c r="G122" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>5</v>
+      </c>
+      <c r="F123" t="s">
+        <v>138</v>
+      </c>
+      <c r="G123" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>5</v>
+      </c>
+      <c r="F124" t="s">
+        <v>138</v>
+      </c>
+      <c r="G124" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125">
+        <v>5</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>5</v>
+      </c>
+      <c r="F125" t="s">
+        <v>138</v>
+      </c>
+      <c r="G125" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B126">
+        <v>5</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>5</v>
+      </c>
+      <c r="F126" t="s">
+        <v>138</v>
+      </c>
+      <c r="G126" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B127">
+        <v>5</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>5</v>
+      </c>
+      <c r="F127" t="s">
+        <v>138</v>
+      </c>
+      <c r="G127" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>5</v>
+      </c>
+      <c r="F128" t="s">
+        <v>138</v>
+      </c>
+      <c r="G128" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129" t="s">
+        <v>138</v>
+      </c>
+      <c r="G129" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B130">
+        <v>9</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>4</v>
+      </c>
+      <c r="F130" t="s">
+        <v>138</v>
+      </c>
+      <c r="G130" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>12</v>
+      </c>
+      <c r="F131" t="s">
+        <v>138</v>
+      </c>
+      <c r="G131" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B132">
+        <v>9</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>4</v>
+      </c>
+      <c r="F132" t="s">
+        <v>138</v>
+      </c>
+      <c r="G132" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>5</v>
+      </c>
+      <c r="F133" t="s">
+        <v>138</v>
+      </c>
+      <c r="G133" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
         <v>6</v>
       </c>
-      <c r="D121" t="s">
-        <v>138</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="F134" t="s">
+        <v>138</v>
+      </c>
+      <c r="G134" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B122">
-        <v>2</v>
-      </c>
-      <c r="C122">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B135">
+        <v>9</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>4</v>
+      </c>
+      <c r="F135" t="s">
+        <v>138</v>
+      </c>
+      <c r="G135" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>12</v>
+      </c>
+      <c r="F136" t="s">
+        <v>138</v>
+      </c>
+      <c r="G136" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>8</v>
+      </c>
+      <c r="F137" t="s">
+        <v>138</v>
+      </c>
+      <c r="G137" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
         <v>6</v>
       </c>
-      <c r="D122" t="s">
-        <v>138</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="F138" t="s">
+        <v>138</v>
+      </c>
+      <c r="G138" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B123">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B139">
+        <v>10</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
         <v>4</v>
       </c>
-      <c r="C123">
-        <v>6</v>
-      </c>
-      <c r="D123" t="s">
-        <v>138</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="F139" t="s">
+        <v>138</v>
+      </c>
+      <c r="G139" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B124">
-        <v>1</v>
-      </c>
-      <c r="C124">
-        <v>12</v>
-      </c>
-      <c r="D124" t="s">
-        <v>138</v>
-      </c>
-      <c r="E124" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B125">
-        <v>1</v>
-      </c>
-      <c r="C125">
-        <v>10</v>
-      </c>
-      <c r="D125" t="s">
-        <v>138</v>
-      </c>
-      <c r="E125" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B126">
-        <v>1</v>
-      </c>
-      <c r="C126">
-        <v>12</v>
-      </c>
-      <c r="D126" t="s">
-        <v>138</v>
-      </c>
-      <c r="E126" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
-        <v>12</v>
-      </c>
-      <c r="D127" t="s">
-        <v>138</v>
-      </c>
-      <c r="E127" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B128">
-        <v>1</v>
-      </c>
-      <c r="C128">
-        <v>12</v>
-      </c>
-      <c r="D128" t="s">
-        <v>138</v>
-      </c>
-      <c r="E128" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B129">
-        <v>1</v>
-      </c>
-      <c r="C129">
-        <v>12</v>
-      </c>
-      <c r="D129" t="s">
-        <v>138</v>
-      </c>
-      <c r="E129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B130">
-        <v>1</v>
-      </c>
-      <c r="C130">
-        <v>12</v>
-      </c>
-      <c r="D130" t="s">
-        <v>138</v>
-      </c>
-      <c r="E130" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="C131">
-        <v>12</v>
-      </c>
-      <c r="D131" t="s">
-        <v>138</v>
-      </c>
-      <c r="E131" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B132">
-        <v>1</v>
-      </c>
-      <c r="C132">
-        <v>12</v>
-      </c>
-      <c r="D132" t="s">
-        <v>138</v>
-      </c>
-      <c r="E132" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B133">
-        <v>1</v>
-      </c>
-      <c r="C133">
-        <v>12</v>
-      </c>
-      <c r="D133" t="s">
-        <v>138</v>
-      </c>
-      <c r="E133" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134">
-        <v>12</v>
-      </c>
-      <c r="D134" t="s">
-        <v>138</v>
-      </c>
-      <c r="E134" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B135">
-        <v>1</v>
-      </c>
-      <c r="C135">
-        <v>12</v>
-      </c>
-      <c r="D135" t="s">
-        <v>138</v>
-      </c>
-      <c r="E135" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="C136">
-        <v>12</v>
-      </c>
-      <c r="D136" t="s">
-        <v>138</v>
-      </c>
-      <c r="E136" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137">
-        <v>5</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137" t="s">
-        <v>138</v>
-      </c>
-      <c r="E137" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138">
-        <v>5</v>
-      </c>
-      <c r="D138" t="s">
-        <v>138</v>
-      </c>
-      <c r="E138" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B139">
-        <v>2</v>
-      </c>
-      <c r="C139">
-        <v>5</v>
-      </c>
-      <c r="D139" t="s">
-        <v>138</v>
-      </c>
-      <c r="E139" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="B140">
         <v>5</v>
       </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140" t="s">
-        <v>138</v>
-      </c>
-      <c r="E140" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>6</v>
+      </c>
+      <c r="F140" t="s">
+        <v>138</v>
+      </c>
+      <c r="G140" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
-      <c r="C141">
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>6</v>
+      </c>
+      <c r="F141" t="s">
+        <v>138</v>
+      </c>
+      <c r="G141" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>6</v>
+      </c>
+      <c r="F142" t="s">
+        <v>138</v>
+      </c>
+      <c r="G142" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s">
+        <v>138</v>
+      </c>
+      <c r="G143" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>10</v>
+      </c>
+      <c r="F144" t="s">
+        <v>138</v>
+      </c>
+      <c r="G144" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145">
+        <v>12</v>
+      </c>
+      <c r="F145" t="s">
+        <v>138</v>
+      </c>
+      <c r="G145" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>12</v>
+      </c>
+      <c r="F146" t="s">
+        <v>138</v>
+      </c>
+      <c r="G146" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>12</v>
+      </c>
+      <c r="F147" t="s">
+        <v>138</v>
+      </c>
+      <c r="G147" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>12</v>
+      </c>
+      <c r="F148" t="s">
+        <v>138</v>
+      </c>
+      <c r="G148" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149">
+        <v>12</v>
+      </c>
+      <c r="F149" t="s">
+        <v>138</v>
+      </c>
+      <c r="G149" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>12</v>
+      </c>
+      <c r="F150" t="s">
+        <v>138</v>
+      </c>
+      <c r="G150" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>12</v>
+      </c>
+      <c r="F151" t="s">
+        <v>138</v>
+      </c>
+      <c r="G151" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>12</v>
+      </c>
+      <c r="F152" t="s">
+        <v>138</v>
+      </c>
+      <c r="G152" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>12</v>
+      </c>
+      <c r="F153" t="s">
+        <v>138</v>
+      </c>
+      <c r="G153" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>12</v>
+      </c>
+      <c r="F154" t="s">
+        <v>138</v>
+      </c>
+      <c r="G154" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>12</v>
+      </c>
+      <c r="F155" t="s">
+        <v>138</v>
+      </c>
+      <c r="G155" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B156">
         <v>5</v>
       </c>
-      <c r="D141" t="s">
-        <v>138</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156" t="s">
+        <v>138</v>
+      </c>
+      <c r="G156" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
+        <v>138</v>
+      </c>
+      <c r="G157" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>5</v>
+      </c>
+      <c r="F158" t="s">
+        <v>138</v>
+      </c>
+      <c r="G158" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B159">
+        <v>5</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159" t="s">
+        <v>138</v>
+      </c>
+      <c r="G159" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>5</v>
+      </c>
+      <c r="F160" t="s">
+        <v>138</v>
+      </c>
+      <c r="G160" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B142">
-        <v>1</v>
-      </c>
-      <c r="C142">
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
         <v>5</v>
       </c>
-      <c r="D142" t="s">
-        <v>138</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F161" t="s">
+        <v>138</v>
+      </c>
+      <c r="G161" t="s">
         <v>135</v>
       </c>
     </row>
